--- a/frontend/internal/DFW_HVAC_Site_Audit.xlsx
+++ b/frontend/internal/DFW_HVAC_Site_Audit.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,6 +36,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
   <fills count="7">
@@ -122,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -145,6 +149,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -510,13 +524,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="80" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="80" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -540,6 +556,16 @@
           <t>Live URL</t>
         </is>
       </c>
+      <c r="E1" s="12" t="inlineStr">
+        <is>
+          <t>Proposed Meta Description (Apr 20, 2026)</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>Char Count</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1010,6 +1036,14 @@
           <t>https://dfwhvac.com/cities-served/allen</t>
         </is>
       </c>
+      <c r="E24" s="14" t="inlineStr">
+        <is>
+          <t>Allen, TX AC &amp; heating repair, install &amp; maintenance. Same-day service. Call (972) 777-2665. Licensed, family-owned. Zip: 75013.</t>
+        </is>
+      </c>
+      <c r="F24" s="15" t="n">
+        <v>128</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -1032,6 +1066,14 @@
           <t>https://dfwhvac.com/cities-served/argyle</t>
         </is>
       </c>
+      <c r="E25" s="14" t="inlineStr">
+        <is>
+          <t>Argyle, TX AC &amp; heating repair, install &amp; maintenance. Same-day service. Call (972) 777-2665. Licensed, family-owned. Zip: 76226.</t>
+        </is>
+      </c>
+      <c r="F25" s="15" t="n">
+        <v>129</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -1054,6 +1096,14 @@
           <t>https://dfwhvac.com/cities-served/arlington</t>
         </is>
       </c>
+      <c r="E26" s="14" t="inlineStr">
+        <is>
+          <t>Arlington, TX AC &amp; heating repair, install &amp; maintenance. Same-day service. Call (972) 777-2665. Licensed, family-owned. Zips: 76001, 76002, 76012 &amp; more.</t>
+        </is>
+      </c>
+      <c r="F26" s="15" t="n">
+        <v>154</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -1076,6 +1126,14 @@
           <t>https://dfwhvac.com/cities-served/bedford</t>
         </is>
       </c>
+      <c r="E27" s="14" t="inlineStr">
+        <is>
+          <t>Bedford, TX AC &amp; heating repair, install &amp; maintenance. Same-day service. Call (972) 777-2665. Licensed, family-owned. Zips: 76021, 76022.</t>
+        </is>
+      </c>
+      <c r="F27" s="15" t="n">
+        <v>138</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -1098,6 +1156,14 @@
           <t>https://dfwhvac.com/cities-served/carrollton</t>
         </is>
       </c>
+      <c r="E28" s="14" t="inlineStr">
+        <is>
+          <t>Carrollton, TX AC &amp; heating repair, install &amp; maintenance. Same-day service. Call (972) 777-2665. Licensed, family-owned. Zips: 75006, 75007, 75010.</t>
+        </is>
+      </c>
+      <c r="F28" s="15" t="n">
+        <v>148</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -1120,6 +1186,14 @@
           <t>https://dfwhvac.com/cities-served/colleyville</t>
         </is>
       </c>
+      <c r="E29" s="14" t="inlineStr">
+        <is>
+          <t>Colleyville, TX AC &amp; heating repair, install &amp; maintenance. Same-day service. Call (972) 777-2665. Licensed, family-owned. Zip: 76034.</t>
+        </is>
+      </c>
+      <c r="F29" s="15" t="n">
+        <v>134</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -1142,6 +1216,14 @@
           <t>https://dfwhvac.com/cities-served/coppell</t>
         </is>
       </c>
+      <c r="E30" s="14" t="inlineStr">
+        <is>
+          <t>Coppell, TX AC &amp; heating repair, install &amp; maintenance. Same-day service. Call (972) 777-2665. Licensed, family-owned. Zip: 75019.</t>
+        </is>
+      </c>
+      <c r="F30" s="15" t="n">
+        <v>130</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -1164,6 +1246,14 @@
           <t>https://dfwhvac.com/cities-served/dallas</t>
         </is>
       </c>
+      <c r="E31" s="14" t="inlineStr">
+        <is>
+          <t>Dallas, TX AC &amp; heating repair, install &amp; maintenance. Same-day service. Call (972) 777-2665. Licensed, family-owned. Zips: 75201, 75202, 75204 &amp; more.</t>
+        </is>
+      </c>
+      <c r="F31" s="15" t="n">
+        <v>151</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -1186,6 +1276,12 @@
           <t>https://dfwhvac.com/cities-served/denton</t>
         </is>
       </c>
+      <c r="E32" s="14" t="inlineStr">
+        <is>
+          <t>(already correct — no change)</t>
+        </is>
+      </c>
+      <c r="F32" s="15" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -1208,6 +1304,14 @@
           <t>https://dfwhvac.com/cities-served/euless</t>
         </is>
       </c>
+      <c r="E33" s="14" t="inlineStr">
+        <is>
+          <t>Euless, TX AC &amp; heating repair, install &amp; maintenance. Same-day service. Call (972) 777-2665. Licensed, family-owned. Zips: 76039, 76040.</t>
+        </is>
+      </c>
+      <c r="F33" s="15" t="n">
+        <v>137</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -1230,6 +1334,14 @@
           <t>https://dfwhvac.com/cities-served/farmers-branch</t>
         </is>
       </c>
+      <c r="E34" s="14" t="inlineStr">
+        <is>
+          <t>Farmers Branch, TX AC &amp; heating repair, install &amp; maintenance. Same-day service. Call (972) 777-2665. Licensed, family-owned. Zip: 75234.</t>
+        </is>
+      </c>
+      <c r="F34" s="15" t="n">
+        <v>137</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -1252,6 +1364,14 @@
           <t>https://dfwhvac.com/cities-served/flower-mound</t>
         </is>
       </c>
+      <c r="E35" s="14" t="inlineStr">
+        <is>
+          <t>Flower Mound, TX AC &amp; heating repair, install &amp; maintenance. Same-day service. Call (972) 777-2665. Licensed, family-owned. Zips: 75022, 75028, 75077.</t>
+        </is>
+      </c>
+      <c r="F35" s="15" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -1274,6 +1394,14 @@
           <t>https://dfwhvac.com/cities-served/fort-worth</t>
         </is>
       </c>
+      <c r="E36" s="14" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX AC &amp; heating repair, install &amp; maintenance. Same-day service. Call (972) 777-2665. Licensed, family-owned. Zips: 76118, 76120, 76137 &amp; more.</t>
+        </is>
+      </c>
+      <c r="F36" s="15" t="n">
+        <v>155</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -1296,6 +1424,14 @@
           <t>https://dfwhvac.com/cities-served/frisco</t>
         </is>
       </c>
+      <c r="E37" s="14" t="inlineStr">
+        <is>
+          <t>Frisco, TX AC &amp; heating repair, install &amp; maintenance. Same-day service. Call (972) 777-2665. Licensed, family-owned. Zips: 75033, 75034, 75035 &amp; more.</t>
+        </is>
+      </c>
+      <c r="F37" s="15" t="n">
+        <v>151</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -1318,6 +1454,14 @@
           <t>https://dfwhvac.com/cities-served/grapevine</t>
         </is>
       </c>
+      <c r="E38" s="14" t="inlineStr">
+        <is>
+          <t>Grapevine, TX AC &amp; heating repair, install &amp; maintenance. Same-day service. Call (972) 777-2665. Licensed, family-owned. Zip: 76051.</t>
+        </is>
+      </c>
+      <c r="F38" s="15" t="n">
+        <v>132</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -1340,6 +1484,14 @@
           <t>https://dfwhvac.com/cities-served/haslet</t>
         </is>
       </c>
+      <c r="E39" s="14" t="inlineStr">
+        <is>
+          <t>Haslet, TX AC &amp; heating repair, install &amp; maintenance. Same-day service. Call (972) 777-2665. Licensed, family-owned. Zip: 76052.</t>
+        </is>
+      </c>
+      <c r="F39" s="15" t="n">
+        <v>129</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -1362,6 +1514,14 @@
           <t>https://dfwhvac.com/cities-served/hurst</t>
         </is>
       </c>
+      <c r="E40" s="14" t="inlineStr">
+        <is>
+          <t>Hurst, TX AC &amp; heating repair, install &amp; maintenance. Same-day service. Call (972) 777-2665. Licensed, family-owned. Zip: 76054.</t>
+        </is>
+      </c>
+      <c r="F40" s="15" t="n">
+        <v>128</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -1384,6 +1544,14 @@
           <t>https://dfwhvac.com/cities-served/irving</t>
         </is>
       </c>
+      <c r="E41" s="14" t="inlineStr">
+        <is>
+          <t>Irving, TX AC &amp; heating repair, install &amp; maintenance. Same-day service. Call (972) 777-2665. Licensed, family-owned. Zips: 75038, 75039, 75062 &amp; more.</t>
+        </is>
+      </c>
+      <c r="F41" s="15" t="n">
+        <v>151</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -1406,6 +1574,14 @@
           <t>https://dfwhvac.com/cities-served/keller</t>
         </is>
       </c>
+      <c r="E42" s="14" t="inlineStr">
+        <is>
+          <t>Keller, TX AC &amp; heating repair, install &amp; maintenance. Same-day service. Call (972) 777-2665. Licensed, family-owned. Zips: 76244, 76248.</t>
+        </is>
+      </c>
+      <c r="F42" s="15" t="n">
+        <v>137</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -1428,6 +1604,14 @@
           <t>https://dfwhvac.com/cities-served/lake-dallas</t>
         </is>
       </c>
+      <c r="E43" s="14" t="inlineStr">
+        <is>
+          <t>Lake Dallas, TX AC &amp; heating repair, install &amp; maintenance. Same-day service. Call (972) 777-2665. Licensed, family-owned. Zip: 75065.</t>
+        </is>
+      </c>
+      <c r="F43" s="15" t="n">
+        <v>134</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -1450,6 +1634,14 @@
           <t>https://dfwhvac.com/cities-served/lewisville</t>
         </is>
       </c>
+      <c r="E44" s="14" t="inlineStr">
+        <is>
+          <t>Lewisville, TX AC &amp; heating repair, install &amp; maintenance. Same-day service. Call (972) 777-2665. Licensed, family-owned. Zips: 75057, 75067.</t>
+        </is>
+      </c>
+      <c r="F44" s="15" t="n">
+        <v>141</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -1472,6 +1664,14 @@
           <t>https://dfwhvac.com/cities-served/mansfield</t>
         </is>
       </c>
+      <c r="E45" s="14" t="inlineStr">
+        <is>
+          <t>Mansfield, TX AC &amp; heating repair, install &amp; maintenance. Same-day service. Call (972) 777-2665. Licensed, family-owned. Zip: 76063.</t>
+        </is>
+      </c>
+      <c r="F45" s="15" t="n">
+        <v>132</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -1494,6 +1694,14 @@
           <t>https://dfwhvac.com/cities-served/north-richland-hills</t>
         </is>
       </c>
+      <c r="E46" s="14" t="inlineStr">
+        <is>
+          <t>North Richland Hills, TX AC &amp; heating repair, install &amp; maintenance. Same-day service. Call (972) 777-2665. Licensed, family-owned. Zips: 76148, 76180, 76182.</t>
+        </is>
+      </c>
+      <c r="F46" s="15" t="n">
+        <v>158</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -1516,6 +1724,14 @@
           <t>https://dfwhvac.com/cities-served/plano</t>
         </is>
       </c>
+      <c r="E47" s="14" t="inlineStr">
+        <is>
+          <t>Plano, TX AC &amp; heating repair, install &amp; maintenance. Same-day service. Call (972) 777-2665. Licensed, family-owned. Zips: 75023, 75024, 75025 &amp; more.</t>
+        </is>
+      </c>
+      <c r="F47" s="15" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -1538,6 +1754,14 @@
           <t>https://dfwhvac.com/cities-served/richardson</t>
         </is>
       </c>
+      <c r="E48" s="14" t="inlineStr">
+        <is>
+          <t>Richardson, TX AC &amp; heating repair, install &amp; maintenance. Same-day service. Call (972) 777-2665. Licensed, family-owned. Zips: 75080, 75081.</t>
+        </is>
+      </c>
+      <c r="F48" s="15" t="n">
+        <v>141</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -1560,6 +1784,14 @@
           <t>https://dfwhvac.com/cities-served/roanoke</t>
         </is>
       </c>
+      <c r="E49" s="14" t="inlineStr">
+        <is>
+          <t>Roanoke, TX AC &amp; heating repair, install &amp; maintenance. Same-day service. Call (972) 777-2665. Licensed, family-owned. Zip: 76262.</t>
+        </is>
+      </c>
+      <c r="F49" s="15" t="n">
+        <v>130</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -1582,6 +1814,14 @@
           <t>https://dfwhvac.com/cities-served/southlake</t>
         </is>
       </c>
+      <c r="E50" s="14" t="inlineStr">
+        <is>
+          <t>Southlake, TX AC &amp; heating repair, install &amp; maintenance. Same-day service. Call (972) 777-2665. Licensed, family-owned. Zip: 76092.</t>
+        </is>
+      </c>
+      <c r="F50" s="15" t="n">
+        <v>132</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -1604,7 +1844,16 @@
           <t>https://dfwhvac.com/cities-served/the-colony</t>
         </is>
       </c>
-    </row>
+      <c r="E51" s="14" t="inlineStr">
+        <is>
+          <t>The Colony, TX AC &amp; heating repair, install &amp; maintenance. Same-day service. Call (972) 777-2665. Licensed, family-owned. Zip: 75056.</t>
+        </is>
+      </c>
+      <c r="F51" s="15" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="52"/>
     <row r="53">
       <c r="A53" s="9" t="inlineStr">
         <is>
@@ -1623,6 +1872,41 @@
       <c r="A55" s="11" t="inlineStr">
         <is>
           <t>Red = Fallback code description (no custom meta description set in CMS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="inlineStr">
+        <is>
+          <t>Template used (Option A — adaptive zip count):</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>"[City], TX AC &amp; heating repair, install &amp; maintenance. Same-day service. Call (972) 777-2665. Licensed, family-owned. [Zip line]."</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Zip line rules: 1 zip -&gt; "Zip: X."  |  2 zips -&gt; "Zips: X, Y."  |  3 zips -&gt; "Zips: X, Y, Z."  |  4+ zips -&gt; "Zips: X, Y, Z &amp; more."</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Yellow fill = char count &gt; 160 (may truncate on desktop SERP, mobile will truncate earlier regardless)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Phone uses dialable digits (972) 777-2665 — required for Google SERP click-to-call. Vanity (972) 777-COOL kept on-site for brand.</t>
         </is>
       </c>
     </row>
